--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-informant.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-informant.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -284,7 +284,7 @@
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-related-person
-https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager</t>
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient</t>
   </si>
   <si>
     <t>L'informateur est un patient/usager ou un autre type d'informateur (ex : aidant, personne à prévenir en cas d'urgence, etc.)</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-informant.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-informant.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
